--- a/daily_matches/job_matches_2026-09-03.xlsx
+++ b/daily_matches/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect, Forward Deployed</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rackspace Technology</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,182 +486,182 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Glue, Athena, Redshift, Data Lake</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, BigQuery, Data Lake, Dataflow, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9f571d1cebb697</t>
+          <t>https://www.indeed.com/viewjob?jk=d327cf6aabca3bf4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>System Engineer – Site Reliability Engineering (SRE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, BigQuery, Data Lake, Dataflow, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c5f0f23e27f447f</t>
+          <t>https://www.indeed.com/viewjob?jk=97c9639c442911cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, BigQuery, Data Lake, Dataflow, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8cba22bfa4507f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5bcfb63295905b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Databricks, Power BI, Python</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, BigQuery, Data Lake, Dataflow, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e46e188f9984b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f700b926bc75474</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PyTorch, OpenCV, Docker, Kubernetes, Jenkins, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, BigQuery, Data Lake, Dataflow, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e249f1007751107</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>AWS DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Kinesis, CI/CD, Terraform, Git, Redshift, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, S3, EC2, Glue, Redshift, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf704911ff39cc0e</t>
+          <t>https://www.indeed.com/viewjob?jk=d29dcd9067394b82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Science Student Experience - Spring 2027</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Bobcat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Buford, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, AKS, CI/CD, Terraform, Git, Snowflake, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, FAISS, Pinecone, S3, Docker, Git, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdbf246fba3b7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dba2a87bf26e0a38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, AKS, CI/CD, Terraform, Git, Snowflake, Python</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2773353d84acb8</t>
+          <t>https://www.indeed.com/viewjob?jk=400bab78fb65e7e1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, AKS, CI/CD, Terraform, Git, Snowflake, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07f4dbbd7f3b0881</t>
+          <t>https://www.indeed.com/viewjob?jk=91924249bc2ffb8e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, AKS, CI/CD, Terraform, Git, Snowflake, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965944ad08ce1aea</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf517a868bb31de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT AI Senior Specialist</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, AKS, CI/CD, Terraform, Git, Snowflake, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd8c6c6438801353</t>
+          <t>https://www.indeed.com/viewjob?jk=6af86766445e845d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Data Scientist II - Big Data R&amp;D, Identity Graph &amp; Deceased Monitoring</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Kafka, MySQL, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, S3, Data Lake, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dee16bdfca5835f</t>
+          <t>https://www.indeed.com/viewjob?jk=241d21dce5d3c25d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47e1714d0067a78a</t>
+          <t>https://www.indeed.com/viewjob?jk=94e187ddd5c7b1c5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Octave</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, BigQuery, Redshift, Python</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c14c404355ce78</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>AI-Enabled Data Architecture Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Bannockburn, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f3b4c6d08a1a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=14313f155351f299</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0e48bddbab8709</t>
+          <t>https://www.indeed.com/viewjob?jk=9196124d928381a7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219891b58fcd2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=561060decdb9c1b4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80690607da1933cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d2f1f44e876585</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4298fc54babb043d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a0dc9b197a197f8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Developer – Python</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fb8147abac9706</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6c8a38a94b0766</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Applied AI ML Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Databricks, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ddd12d228f456b</t>
+          <t>https://www.indeed.com/viewjob?jk=b63a3a63ab71cdee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (Java)</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0554a871816421df</t>
+          <t>https://www.indeed.com/viewjob?jk=18fa67b62a9bcf6f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0cb10d0e8883c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e704eb45c41f12b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0975812eb49b197</t>
+          <t>https://www.indeed.com/viewjob?jk=b77cb7394a6ce601</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II, AI Labs &amp; Foundations</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fad9852d645513</t>
+          <t>https://www.indeed.com/viewjob?jk=7e68a257aab00b89</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b64678e3b104717</t>
+          <t>https://www.indeed.com/viewjob?jk=14e9f8548759ebe0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist, FP&amp;A Solutions</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5549080bb45b63f</t>
+          <t>https://www.indeed.com/viewjob?jk=7258196f051c4d4e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-1</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Lake, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2590134101b4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=186a1cd445c4b75b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mobile Engineer, Senior</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14a19eaf76410bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a19f9173b106c62d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Analysis Engineering Tools</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3105ac11c39e4</t>
+          <t>https://www.indeed.com/viewjob?jk=344754650014b59d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Nebraska</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FastAPI, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5a7a4f938c35ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8f5bca99461b84</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forward-Deployed Solutions Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e50397c10283e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ba1c989a5984ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FormAssembly inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c24161470b80b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd36b19d5640d1a4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Git, Snowflake, Redshift, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd798526a8517585</t>
+          <t>https://www.indeed.com/viewjob?jk=91a93750d1830592</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f6475f681696fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=32b0c0fb92af5a07</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cable One</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd677fc5d696303</t>
+          <t>https://www.indeed.com/viewjob?jk=9eb4e03ddc61f32d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Digital Workplace Engineer IV</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d553f2f40ea9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=9495207c7faba18e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Simulations Plus, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d1ade33ae3b32</t>
+          <t>https://www.indeed.com/viewjob?jk=b37b385267f9ede4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mobile Engineer, Consultant</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb2d3b6a6ca8f72</t>
+          <t>https://www.indeed.com/viewjob?jk=71000be271fb9358</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Solutions Analyst and Engineering Support</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MAERSK</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, PostgreSQL, Power BI, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d5a586c4120e68</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd78e750dee90a5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>US - Analytics Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shriners Children's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, CI/CD, Databricks, PySpark, Power BI, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77660b2eea076545</t>
+          <t>https://www.indeed.com/viewjob?jk=4c56a46da8d3729b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Software Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843624eb89c6e992</t>
+          <t>https://www.indeed.com/viewjob?jk=21710804828c2f63</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tria Federal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef90c3b97bbb264c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ef2713a4800cbf6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Healthfirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1515fa505b38750</t>
+          <t>https://www.indeed.com/viewjob?jk=f60fef5407b89437</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Computer Vision and Data Analysis Co-Op</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, YOLO, Git, Python, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986c7b8df15e58ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bde333de098d896b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Associate (+ SAP ) Consultant t</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,42 +2071,1337 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d68c59df1bfd475</t>
+          <t>https://www.indeed.com/viewjob?jk=672df186a4ed8368</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Financial Reporting Technical Analyst</t>
+          <t>Associate AI Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0935cd17951730cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d87644a26218f75</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6dc9bdc5ba41130</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bff1638e71be5b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54ef24abc7b2678e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bc85b096ac0834f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7eccb1e8f658e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Associate AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e51028588e9949f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer-Marketplace</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Staples</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Framingham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Kubernetes, AKS, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a620a3ac2e856ed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>People Analytics and AI Intern</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Cortex, Dataflow, Snowflake, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc710cb2e6bf5f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Aramark</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f087a7f276c81325</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>WellSky</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Terraform, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67e47d72a1964051</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Engineer IV- 4P/619</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4P Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, CI/CD, Git, Databricks, NoSQL, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d259dc9b8605334b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java or Python) - Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Zimperium</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebf4b017247c8e62</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Engineer (Langchain)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c469cf2bbb840063</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Langchain Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=641fa289e0470e8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - Application Security</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5064e68358dfe6b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - Application Security</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f6f58d44c80333</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - Application Security</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e375826212796114</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - Application Security</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed027a3c50f2ec47</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - Application Security</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65849f58bd4ad5e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - Application Security</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18a7f5a99c82752b</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - Application Security</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b204a450dddd76a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI Applied Scientist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Verily</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>San Bruno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f13b3a2d714129b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Data Scientist, NA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176368778bfec6b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Internship, Software Engineer, AI Data Infrastructure (Winter/Spring 2027)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>10</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fddbe9d5178d0ccd</t>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92dfb03df9e2e47f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - NBA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76a3ad94329ae20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Immunetrics, Inc.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=582a0ea7fe1897f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Mgr. Software Engineering, GWS Automation</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=208b00ab16b39b97</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Engineering Architect, Senior</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bloomberg Industry Group</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6f6871e7815e508</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II (Intern) - United States</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, LLaMA, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d0b766deac680ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Generac Power Systems</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Waukesha, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00fd1c337ba22e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Akron, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, AKS, Git, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01375514b217e3ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, AKS, Git, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62045274597603a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CESO, Inc.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, AKS, Git, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27c86305f5a4b4d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Lowe's Home Improvement</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, MLflow, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c9522c0122d2262</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c4f9637207dc113</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sr. Mgr. Software Engineering, GWS Automation</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52034e9a41596771</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-03.xlsx
+++ b/daily_matches/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer &amp; Developer, Security Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Snowflake, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcff22cb22d06c48</t>
+          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Specialist Data Scientist</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Docker, Apache Airflow, Git, Databricks, Hadoop</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec282dae7af743d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c09951808317e807</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ML Ops Generative AI Engineer</t>
+          <t>Computing Engineer/Software Developer –AI/ML, GUI Development, Custom Cobot Control</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>Custom Manufacturing and Engineering</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pinellas Park, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e962b451ead9059</t>
+          <t>https://www.indeed.com/viewjob?jk=e97b8b145647f2bc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps &amp; Data Engineer</t>
+          <t>Data Engineer Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sierra Nevada Corporation</t>
+          <t>Indicium AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lone Tree, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, S3, EC2, Glue, Athena, Redshift, MLflow, Kubernetes, CI/CD</t>
+          <t>Redshift, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Databricks, Redshift, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d119b132aefd5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VAMS Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas-Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, Glue, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>Generative AI, RAG, LLaMA, Mistral, Pinecone, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27a794ae5abed1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=efbac98dfc6279b2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde5d548962c6033</t>
+          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior AI/ML Engineer – Healthcare AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c46e528a9b82e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1354b83051ed6e15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Scientist - Generative BI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82ef84e533fce6b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e3c7fd16bcae49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Associate Data Scientist - Generative BI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f471a8c43f304fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d812f5d3973914</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Salesforce AI Engineer</t>
+          <t>Senior Software Engineer (Full Stack - Node.js, React, MongoDB)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Maryland City, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
+          <t>Generative AI, Copilot, Docker, Kubernetes, Git, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866612a4a0a6df11</t>
+          <t>https://www.indeed.com/viewjob?jk=e281c37da06c013a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analyst, Analytics and Visualization Engineer</t>
+          <t>Senior Software Engineer (Full Stack - Node.js, React, MongoDB)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Choice Hotels</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Virginia, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, Redshift, Git, Redshift, Tableau, Python, SQL</t>
+          <t>Generative AI, Copilot, Docker, Kubernetes, Git, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b40e66f02dd7f61</t>
+          <t>https://www.indeed.com/viewjob?jk=75eece114bbbeccc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Translational AI Engineer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, CI/CD, Git, Python</t>
+          <t>RAG, Synapse, Data Lake, Databricks, Hadoop, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffee49562b40392c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empower AI Inc.</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, Databricks, Hadoop, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4b2cf987ee6dff4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer, Analyst – Data Analytics &amp; AI</t>
+          <t>Technology Partner - Databricks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, Docker, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Data Lake, Databricks, Hadoop, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,392 +951,42 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc38f3715c05c61</t>
+          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer, Associate – Data Analytics &amp; AI</t>
+          <t>Mgr. Software Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, Docker, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2663a4b4b73da8ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ncontracts</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Redshift, Data Lake, CI/CD, Git, Snowflake, Redshift, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=997cf829733bcc11</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Java AWS Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acae8b3a9f218a11</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sr. Engineer, AI Platforms and Solutions</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6f0475a6307fe9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Associate Scientist, Upstream Process Development — Bioprocess Automation &amp; Digitization</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Pfizer</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Andover, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, GitHub Actions, Git, Snowflake, PostgreSQL, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1412138db994207</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer – Software / Infrastructure / AI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fcd70914599b88</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Rotational Program Development Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>VIAVI Solutions</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Hugging Face, Docker, Kubernetes, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7a24e688a883b45d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Scientist - Pricing &amp; Profitability</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Snowflake, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb0de9c8aa43341</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Azure Platform</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a738da303dc8ffd2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Gap Inc.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, AWS SageMaker, Azure ML, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4351def639841002</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Associate (+ SAP ) Consultant t</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15ad35828f2dddf5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ef7169c1d8405</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-03.xlsx
+++ b/daily_matches/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badf8a963d8c46e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a7add4f2eb5620f9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GenAI Architect</t>
+          <t>Java Developer with AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Copilot, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09951808317e807</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Computing Engineer/Software Developer –AI/ML, GUI Development, Custom Cobot Control</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Custom Manufacturing and Engineering</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pinellas Park, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97b8b145647f2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer Consultant</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, Apache Airflow, CI/CD, Terraform, Git, Snowflake, Databricks, Redshift, PySpark, Kafka</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72cc11f621d19b31</t>
+          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VAMS Technologies</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas-Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Mistral, Pinecone, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbac98dfc6279b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac357ad96cce2a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer – Healthcare AI</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1354b83051ed6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Generative BI</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e3c7fd16bcae49</t>
+          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data Scientist - Generative BI</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d812f5d3973914</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack - Node.js, React, MongoDB)</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Maryland City, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, Git, MongoDB, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e281c37da06c013a</t>
+          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack - Node.js, React, MongoDB)</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Virginia, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, Git, MongoDB, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eece114bbbeccc</t>
+          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Databricks, Hadoop, NoSQL, SQL, R, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf367eb9c34a5aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Databricks, Hadoop, NoSQL, SQL, R, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb19697ac2324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Technology Partner - Databricks</t>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Databricks, Hadoop, NoSQL, SQL, R, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,602 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f0fe6cc0a92eea</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mgr. Software Engineering</t>
+          <t>Sr. Systems Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Datavations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. Full-Stack Engineer, Data Systems</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Datavations</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Edgewater Federal Solutions</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Terraform, Git, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2d71f3740aa0ae6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior GenAI/Python Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, Git, Snowflake</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0623e88a071b101a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Forward Deployed Data Engineer - Houston</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Indicium AI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, AKS, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Strategic Insights Analyst</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>K Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=136f789756026ee7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cloud Data Platform Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>relationalAi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, AKS, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5a2fe9338d87954</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Careers - Job Details (redesign)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Maximus</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bacdcba72cd71ae0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Operations (Agency Temp)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SCAN Health Plan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Long Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=159c1d666a7fb765</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist - Generative BI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dad51796fb7ea59</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BigHat Biosciences</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ef7169c1d8405</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, PyTorch, CI/CD, Git, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ac44b275ba04c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer, Associate (NJUS)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NetJets</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b13e6796b291247</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c3ef164e0cee515</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a5736779e2314ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ea31dde93560d18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>First Bank</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9f23eff636c2fa5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-03.xlsx
+++ b/daily_matches/job_matches_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7add4f2eb5620f9</t>
+          <t>https://www.indeed.com/viewjob?jk=0704cc50203806f0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Developer with AI</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Copilot, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad70f5252874459</t>
+          <t>https://www.indeed.com/viewjob?jk=d16fe09bccc98449</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>AI Architect/AI Engineer – Generative &amp; Agentic AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f31e5aee79b0cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=e230e6b78a548b8f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>AI Engineer – GenAI Application Development</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=605237c86e8d6cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=d03da3576e93ab5a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Developer - AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, S3, EC2, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a7172a180e4e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=16c7307c5a0e8d1d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Full Stack Engineer (Java)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879aa2fe95ffd1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7a912adddfab10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>RAG, PyTorch, OpenCV, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1386ca20434d1b60</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfee380ff72d429</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Senior Data Engineer – Customer AI Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>AI Engineer, Data Scientist, S3, Glue, Athena, Redshift, Git, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546567a58ff8626</t>
+          <t>https://www.indeed.com/viewjob?jk=4be9270d45b614e7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Sr. Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, Jenkins, Git, MySQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb0d86ff2285bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2e85c21a66a6ee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742c349909b06a2</t>
+          <t>https://www.indeed.com/viewjob?jk=13eee2c3860431bb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>RAG, Glue, Athena, Data Lake, Docker, Terraform, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e414d12f00360b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c42860a51728f88f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Tableau Developer &amp; Data Analyst with AI/GenAI Skills(GC AND USC ONLY)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>CAPY Tech Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353a199b50413e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=91088a866a42eb62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>Cyber Security Engineer - Automation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b1adbe5345b50a</t>
+          <t>https://www.indeed.com/viewjob?jk=0bdadf15bcddb227</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>JobSiteCare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6dd04c768962eb</t>
+          <t>https://www.indeed.com/viewjob?jk=53647361cafcb4a7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5de746c06a43a11d</t>
+          <t>https://www.indeed.com/viewjob?jk=1752a88f6c3fbc2f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Full-Stack Engineer, Data Systems</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, BigQuery, Tableau</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c621205c49ede</t>
+          <t>https://www.indeed.com/viewjob?jk=14a69db0ff4b753b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Docker, CI/CD, Terraform, Git, NoSQL, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d71f3740aa0ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=7aafb41883c222e7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior GenAI/Python Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0623e88a071b101a</t>
+          <t>https://www.indeed.com/viewjob?jk=d5d0e92799270894</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer - Houston</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Indicium AI</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, AKS, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81609495aaa654a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa817ef77e0621</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Strategic Insights Analyst</t>
+          <t>Senior Client Quant Specialist, Enterprise Sales - Bloomberg Financial Solutions</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>K Health</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Git, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=136f789756026ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=d336f6adbc86c495</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>Sr. Product Owner</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>DCM Infotech Ltd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea0f16ea9f7bc21</t>
+          <t>https://www.indeed.com/viewjob?jk=0adfed68334dcbbe</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Sr. Cyber Security Engineer - Automation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>relationalAi</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, AKS, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a2fe9338d87954</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd974acb38b1c48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Careers - Job Details (redesign)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Everseen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>PyTorch, OpenCV, Glue, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bacdcba72cd71ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=076708e596883bbc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Operations (Agency Temp)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Jefferson Center for Mental Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Wheat Ridge, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=159c1d666a7fb765</t>
+          <t>https://www.indeed.com/viewjob?jk=fc127508efd8cf45</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist - Generative BI</t>
+          <t>Senior Business Analyst – Customer AI Automation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Git, Databricks, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, Git, Tableau, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dad51796fb7ea59</t>
+          <t>https://www.indeed.com/viewjob?jk=b367a835da475c04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BigHat Biosciences</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, PyTorch, CI/CD, Git, Python, R, Optimization, Bayesian</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ac44b275ba04c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9406dad681de58a8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Associate (NJUS)</t>
+          <t>Senior Backend Software Engineer - Core Backend, Cloud Customer Experience</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NetJets</t>
+          <t>CRUSOE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b13e6796b291247</t>
+          <t>https://www.indeed.com/viewjob?jk=d115be160b60b91e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Professional Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>First Bank</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>S3, Glue, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3ef164e0cee515</t>
+          <t>https://www.indeed.com/viewjob?jk=6da0f05b1b205dac</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Forward Deployed Engineer, Enterprise AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>First Bank</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Beverly Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>AI Engineer, RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a5736779e2314ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0dbb60c36b7c50</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Full Stack Software Engineer - AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>First Bank</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>S3, Docker, CI/CD, Git, Snowflake, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,42 +1511,812 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea31dde93560d18</t>
+          <t>https://www.indeed.com/viewjob?jk=61a673ea62bb8897</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>First Bank</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Quicksight, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07c0ab7711982757</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=377993b84a0ec98e</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Everseen</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20eb1f6ae9257a4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Engineer (AI Service Engines &amp; Integration)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Evolent</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38decfb3603191fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Datavations</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae17a189650c4d87</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Datavations</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=618f18213a2a441f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Datavations</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a817593e6443317</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Datavations</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc7da8481306f15b</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Datavations</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf00cb3c7724215</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Datavations</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Terraform, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7737082ff88ade09</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Data Lake, Git, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1c329395e899e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Associate Actuary</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Wildfire Defense Systems</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bozeman, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acfe24562dfa1c33</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Engineer 2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Catalyst Brands</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f23eff636c2fa5</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=426c144436953b84</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ozmo</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17c4e23b94282540</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Development Engineer I</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Clearwater Analytics (CWAN)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FastAPI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3a80037698cecb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer – Generative &amp; Agentic AI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cencora</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, CI/CD, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0bc18c72046199a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Context Layer Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, Hadoop, MySQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fc37125ae41c912</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Developer - AI Engineering</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Dell Technologies</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, Prompt Engineering, CI/CD, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dda56301efc44ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Advisor Product Developer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Gainwell Technologies LLC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Glue, CI/CD, Terraform, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=396863b3d962a00e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Context Layer Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Kafka, Hadoop, MySQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eed136ebeb1767d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, FAISS, Pinecone, Data Lake, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de049fb996c23f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Engineer, Battery Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Data Lake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f10345042905151b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Scientist - Decision Science &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=141925998de999ef</t>
         </is>
       </c>
     </row>
